--- a/survey_templates/029_library_book_acquisition_voting_form--survey_templates.xlsx
+++ b/survey_templates/029_library_book_acquisition_voting_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,12 +692,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,12 +725,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'title':_'survey_templates'}</t>
+          <t>survey_templates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'title': 'Survey Templates'}</t>
+          <t>Survey Templates</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'title':_'librarian_forms'}</t>
+          <t>librarian_forms</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'title': 'Librarian Forms'}</t>
+          <t>Librarian Forms</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'title':_'romance'}</t>
+          <t>romance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'title': 'Romance'}</t>
+          <t>Romance</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'title':_'mystery'}</t>
+          <t>mystery</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'title': 'Mystery'}</t>
+          <t>Mystery</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'title':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'title': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'title':_'non-fiction'}</t>
+          <t>non-fiction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'title': 'Non-Fiction'}</t>
+          <t>Non-Fiction</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'title':_'biography'}</t>
+          <t>biography</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'title': 'Biography'}</t>
+          <t>Biography</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'title':_'fantasy'}</t>
+          <t>fantasy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'title': 'Fantasy'}</t>
+          <t>Fantasy</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'title':_'science_fiction'}</t>
+          <t>science_fiction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'title': 'Science Fiction'}</t>
+          <t>Science Fiction</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'title':_'graphic_novel'}</t>
+          <t>graphic_novel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'title': 'Graphic Novel'}</t>
+          <t>Graphic Novel</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'title':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'title': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'title':_'poetry'}</t>
+          <t>poetry</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'title': 'Poetry'}</t>
+          <t>Poetry</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'title':_'humor'}</t>
+          <t>humor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'title': 'Humor'}</t>
+          <t>Humor</t>
         </is>
       </c>
     </row>
@@ -946,29 +946,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'title':_'horror'}</t>
+          <t>horror</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'title': 'Horror'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>form_description_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'title':_'science'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'title': 'Science'}</t>
+          <t>Horror</t>
         </is>
       </c>
     </row>
